--- a/sheets/대금율보/검수/잦은난봉가.xlsx
+++ b/sheets/대금율보/검수/잦은난봉가.xlsx
@@ -3611,8 +3611,7 @@
         <is>
           <t xml:space="preserve">潢
 –無
-林仲
-‹</t>
+林仲</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -3624,8 +3623,7 @@
         <is>
           <t xml:space="preserve">潢
 –無
-林仲
-‹</t>
+林仲</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
@@ -3635,8 +3633,7 @@
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-‹</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="G10" s="24" t="inlineStr">
@@ -3646,8 +3643,7 @@
       </c>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-‹</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="I10" s="24" t="inlineStr">
@@ -4011,8 +4007,7 @@
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -4024,8 +4019,7 @@
         <is>
           <t xml:space="preserve">潢
 –無
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="E18" s="24" t="inlineStr">
@@ -4035,8 +4029,7 @@
       </c>
       <c r="F18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="G18" s="24" t="inlineStr">
@@ -4046,8 +4039,7 @@
       </c>
       <c r="H18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I18" s="24" t="inlineStr">

--- a/sheets/대금율보/검수/잦은난봉가.xlsx
+++ b/sheets/대금율보/검수/잦은난봉가.xlsx
@@ -3230,20 +3230,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="86.96" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="97.23" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="97.23" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="I4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="97.23" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="97.23" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="97.23" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="97.23" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="97.23" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="97.23" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="97.23" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="97.23" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="97.23" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="97.23" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="97.23" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="97.23" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="97.23" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="97.23" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -4054,6 +4054,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="77"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="46"/>
 </worksheet>
 </file>